--- a/Result/profitability/5488.xlsx
+++ b/Result/profitability/5488.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0125</v>
+        <v>-0.001250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>12.73625</v>
+        <v>12.715</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03375</v>
+        <v>0.03875</v>
       </c>
       <c r="N3" t="n">
-        <v>12.15</v>
+        <v>12.2875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03749999999999999</v>
+        <v>0.0275</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5425</v>
+        <v>11.21</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.97</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08624999999999999</v>
+        <v>-0.11375</v>
       </c>
       <c r="N5" t="n">
-        <v>9.741250000000001</v>
+        <v>9.631250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0925</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.87875</v>
+        <v>9.32375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07124999999999999</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>9.091249999999999</v>
+        <v>8.09</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04125</v>
+        <v>-0.06</v>
       </c>
       <c r="N8" t="n">
-        <v>8.209999999999999</v>
+        <v>7.411249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.16</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02125</v>
+        <v>-0.02124999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>8.623749999999999</v>
@@ -2026,7 +2026,7 @@
         <v>-0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02249999999999999</v>
+        <v>0.02250000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>10.2975</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>247</v>
+      </c>
+      <c r="D75" t="n">
+        <v>218</v>
+      </c>
+      <c r="E75" t="n">
+        <v>29</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.49125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.389999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3510989010989011</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.879999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0693459416863671</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
